--- a/akadeemiline_kalender.xlsx
+++ b/akadeemiline_kalender.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8474a192ac48de35/Documents/Koolitused/BCS_andmetarkus_2025/Andmetarkus_git/FinalProject/Töökaust/students_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{720AF493-EA72-41D1-8F42-2B20EF5F4BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{720AF493-EA72-41D1-8F42-2B20EF5F4BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A00A152-3484-4219-9AD2-DB02DE722479}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32910" yWindow="1260" windowWidth="21600" windowHeight="11835" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leht 1" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leht 1'!$A$1:$E$15</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -139,12 +150,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -159,14 +176,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -178,6 +189,24 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,265 +545,265 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="22.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="8">
         <v>43710</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="9">
         <v>43863</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="8">
         <v>43723</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="8">
         <v>43864</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="9">
         <v>44003</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="8">
         <v>43876</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>44074</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>44227</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>44089</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>44228</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>44367</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>44242</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="9">
         <v>44438</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="9">
         <v>44591</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="8">
         <v>44454</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="9">
         <v>44592</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="9">
         <v>44731</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="8">
         <v>44607</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>44802</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>44955</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>44819</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>44956</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>45095</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>44972</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="8">
         <v>45173</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="8">
         <v>45326</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="8">
         <v>45184</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="8">
         <v>45327</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="9">
         <v>45466</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="8">
         <v>45337</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>45537</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>45690</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>45915</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>45691</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>45830</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <v>45703</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="9">
         <v>45901</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="9">
         <v>46054</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="8">
         <v>45915</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="9">
         <v>46055</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="9">
         <v>46194</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="8">
         <v>45703</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="10" t="s">
         <v>24</v>
       </c>
     </row>
